--- a/artfynd/A 51289-2023 artfynd.xlsx
+++ b/artfynd/A 51289-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,399 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133716359</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>499352</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6785536</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133716494</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>499357</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6785509</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133715165</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>499306</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6785523</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133716098</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>499268</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6785611</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51289-2023 artfynd.xlsx
+++ b/artfynd/A 51289-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>133716359</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133716494</v>
       </c>
       <c r="B5" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>133716098</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51289-2023 artfynd.xlsx
+++ b/artfynd/A 51289-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133715666</v>
       </c>
       <c r="B2" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133715349</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>133716359</v>
       </c>
       <c r="B4" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133716494</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>133715165</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>133716098</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51289-2023 artfynd.xlsx
+++ b/artfynd/A 51289-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>133715349</v>
       </c>
       <c r="B3" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>133716359</v>
       </c>
       <c r="B4" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133716494</v>
       </c>
       <c r="B5" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>133715165</v>
       </c>
       <c r="B6" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>133716098</v>
       </c>
       <c r="B7" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51289-2023 artfynd.xlsx
+++ b/artfynd/A 51289-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>133716359</v>
       </c>
       <c r="B4" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133716494</v>
       </c>
       <c r="B5" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>133716098</v>
       </c>
       <c r="B7" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51289-2023 artfynd.xlsx
+++ b/artfynd/A 51289-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>133716359</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133716494</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>133716098</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51289-2023 artfynd.xlsx
+++ b/artfynd/A 51289-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133715666</v>
+        <v>133714902</v>
       </c>
       <c r="B2" t="n">
-        <v>8460</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vasseln, Vasseln, Dlr</t>
+          <t>Vasseln, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499300</v>
+        <v>499349</v>
       </c>
       <c r="R2" t="n">
-        <v>6785541</v>
+        <v>6785501</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +747,9 @@
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,62 +764,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133715349</v>
+        <v>133714949</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vasseln, Vasseln, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499300</v>
+        <v>499338</v>
       </c>
       <c r="R3" t="n">
-        <v>6785541</v>
+        <v>6785511</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -862,7 +846,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +856,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sparsamt på vissa tallar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,14 +888,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133716359</v>
+        <v>133716098</v>
       </c>
       <c r="B4" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -934,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>499352</v>
+        <v>499268</v>
       </c>
       <c r="R4" t="n">
-        <v>6785536</v>
+        <v>6785611</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,14 +985,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133716494</v>
+        <v>133716359</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1031,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499357</v>
+        <v>499352</v>
       </c>
       <c r="R5" t="n">
-        <v>6785509</v>
+        <v>6785536</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,50 +1082,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133715165</v>
+        <v>133716494</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vasseln, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499306</v>
+        <v>499357</v>
       </c>
       <c r="R6" t="n">
-        <v>6785523</v>
+        <v>6785509</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,45 +1179,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133716098</v>
+        <v>133715165</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Vasseln, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>499268</v>
+        <v>499306</v>
       </c>
       <c r="R7" t="n">
-        <v>6785611</v>
+        <v>6785523</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,6 +1278,765 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133715349</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vasseln, Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>499300</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6785541</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133715141</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vasseln, Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>499338</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6785511</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133715321</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>499273</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6785551</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133715666</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vasseln, Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>499300</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6785541</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133716025</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vasseln, Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>499259</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6785581</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133716044</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>499271</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6785590</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133716389</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vasseln, Vasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>499360</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6785520</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Peter Turander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Peter Turander, Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51289-2023 artfynd.xlsx
+++ b/artfynd/A 51289-2023 artfynd.xlsx
@@ -1824,7 +1824,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander, Peter Turander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 51289-2023 artfynd.xlsx
+++ b/artfynd/A 51289-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133714902</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133714949</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133716098</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133716359</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133716494</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133715165</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133715349</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,6 +1542,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133715141</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1604,6 +1649,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133715321</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1716,6 +1766,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133715666</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1828,6 +1883,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133716025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1930,6 +1990,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133716044</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2037,8 +2102,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133716389</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>